--- a/outputs/gebaeudemodell/npro_type_mapping.xlsx
+++ b/outputs/gebaeudemodell/npro_type_mapping.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
-    <t xml:space="preserve">Gebäudetyp - gdf</t>
+    <t xml:space="preserve">NutzungArt - gdf</t>
   </si>
   <si>
     <t xml:space="preserve">Funktion - gdf</t>
